--- a/data/banco_boi_preto.xlsx
+++ b/data/banco_boi_preto.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,11 @@
           <t>Tempo Finisher Boi Preto</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Transcrição</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -482,6 +487,7 @@
           <t>17:50:00</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -509,6 +515,7 @@
           <t>17:50:00</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -534,6 +541,87 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>17:50:00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2e2dffd9-914e-4ba0-8576-434513b0eb8a</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-25T13:07:07</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Prefiro não informar</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>eba244a4-193d-4aee-a329-6194b561107d</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-25T13:11:36</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Prefiro não informar</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Eu já fiz a La Mission em 80 km em 17 horas, já fiz a WTR em 3 horas, a prova de 27K.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1c1453ed-c0ff-49c1-8e99-fc5adc0f2d82</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-25T13:15:08</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Prefiro não informar</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fiz a prova da La Mission, 80 km com 1.200, fiz a prova da WTR Nova Lima de 27K com 1.000 de ganho.</t>
         </is>
       </c>
     </row>
@@ -548,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,6 +789,144 @@
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2e2dffd9-914e-4ba0-8576-434513b0eb8a</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prova da La Mission</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>80 km</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+5.511 m</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>17 horas</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>eba244a4-193d-4aee-a329-6194b561107d</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>La Mission</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>80 km</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+3310 m</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>17 horas</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>eba244a4-193d-4aee-a329-6194b561107d</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WTR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3 horas</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>eba244a4-193d-4aee-a329-6194b561107d</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prova de 27K</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>27K</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1c1453ed-c0ff-49c1-8e99-fc5adc0f2d82</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>La Mission</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>80 km</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1200 m</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1c1453ed-c0ff-49c1-8e99-fc5adc0f2d82</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>WTR Nova Lima</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>27 km</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1000 m</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
